--- a/client/public/artefactos/ADI-07.xlsx
+++ b/client/public/artefactos/ADI-07.xlsx
@@ -1908,66 +1908,106 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SQL Server 2017</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>SQL Server 2012</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SQL_Latin1_General_CP1_CI_AS</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>138644.31</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>55.25</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>dbo.aud</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>66.27</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1665.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>ONPSRVPRDSQL17</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5629.45</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>3609.15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1982,106 +2022,66 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SQL Server 2012</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>SQL Server 2017</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SQL_Latin1_General_CP1_CI_AS</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>55.25</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5.47</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>138644.31</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>dbo.aud</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>66.27</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1665.67</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ONPSRVPRDSQL17</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5629.45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3609.15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/client/public/artefactos/ADI-07.xlsx
+++ b/client/public/artefactos/ADI-07.xlsx
@@ -1908,106 +1908,66 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SQL Server 2012</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>SQL Server 2017</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SQL_Latin1_General_CP1_CI_AS</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>55.25</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5.47</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>138644.31</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>dbo.aud</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>66.27</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1665.67</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ONPSRVPRDSQL17</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5629.45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3609.15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2022,46 +1982,98 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SQL Server 2017</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>SQL Server 2019</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Modern_Spanish_CI_AS</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>138644.31</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>dbo.aud</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1665.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>SRVWNPSDBPR01</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2069,17 +2081,17 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5629.45</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3609.15</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>49.7</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2108,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SQL Server 2019</t>
+          <t>SQL Server 2012</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2111,22 +2123,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Modern_Spanish_CI_AS</t>
+          <t>SQL_Latin1_General_CP1_CI_AS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>55.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2136,12 +2148,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2151,7 +2163,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2166,12 +2178,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2187,27 +2199,15 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SRVWNPSDBPR01</t>
+          <t>ONPSRVPRDSQL17</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>149.8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/client/public/artefactos/ADI-07.xlsx
+++ b/client/public/artefactos/ADI-07.xlsx
@@ -1908,46 +1908,98 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SQL Server 2017</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>SQL Server 2019</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Modern_Spanish_CI_AS</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>138644.31</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>dbo.aud</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1665.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ONPBDONPPR01</t>
+          <t>SRVWNPSDBPR01</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1955,17 +2007,17 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5629.45</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3609.15</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>49.7</t>
         </is>
       </c>
     </row>
@@ -1982,98 +2034,46 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SQL Server 2019</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>SQL Server 2017</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Producción</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Modern_Spanish_CI_AS</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>138644.31</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>dbo.aud</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1665.67</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SRVWNPSDBPR01</t>
+          <t>ONPBDONPPR01</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2081,17 +2081,17 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>5629.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>3609.15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>64.1</t>
         </is>
       </c>
     </row>
@@ -13398,12 +13398,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SQL Server 2008 R2</t>
+          <t>SQL Server 2022</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13418,17 +13418,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13438,12 +13438,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>929</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>dbo.SIG_MOVIMIENTO_CONTABLE</t>
+          <t>dbo.CATALOGO_BIEN_SERV_ORIGINAL</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>ONPSRVSMEF</t>
+          <t>SRVWNSMEFPR01</t>
         </is>
       </c>
       <c r="W117" t="inlineStr"/>
@@ -13502,12 +13502,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>9.2</t>
         </is>
       </c>
     </row>
@@ -13524,12 +13524,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SQL Server 2022</t>
+          <t>SQL Server 2008 R2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13544,17 +13544,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>938</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>196</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>dbo.CATALOGO_BIEN_SERV_ORIGINAL</t>
+          <t>dbo.SIG_MOVIMIENTO_CONTABLE</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SRVWNSMEFPR01</t>
+          <t>ONPSRVSMEF</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>70</t>
         </is>
       </c>
     </row>

--- a/client/public/artefactos/ADI-07.xlsx
+++ b/client/public/artefactos/ADI-07.xlsx
@@ -8454,11 +8454,7 @@
           <t>EVENT</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>DB2 v9.5.0.9</t>
@@ -8524,7 +8520,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ONPBMONDBP01</t>
+          <t>ONPWPSDBP01</t>
         </is>
       </c>
       <c r="X66" t="inlineStr"/>
@@ -8532,17 +8528,17 @@
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>119.86</t>
+          <t>353.26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8553,11 @@
           <t>EVENT</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>DB2 v9.5.0.9</t>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>ONPWPSDBP01</t>
+          <t>ONPBMONDBP01</t>
         </is>
       </c>
       <c r="X67" t="inlineStr"/>
@@ -8631,17 +8631,17 @@
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>353.26</t>
+          <t>119.86</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.3</t>
         </is>
       </c>
     </row>
@@ -10294,10 +10294,14 @@
           <t>MONITOR</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DB2 v10.5.0.4</t>
+          <t>DB2 v9.5.0.9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -10307,32 +10311,76 @@
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>ONPBMDBP01</t>
+          <t>ONPBMONDBP01</t>
         </is>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>119.86</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10345,14 +10393,10 @@
           <t>MONITOR</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DB2 v9.5.0.9</t>
+          <t>DB2 v10.5.0.4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -10362,76 +10406,32 @@
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
-          <t>ONPBMONDBP01</t>
+          <t>ONPBMDBP01</t>
         </is>
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>119.86</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13166,10 +13166,14 @@
           <t>RESDB</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DB2 v10.1.0.5</t>
+          <t>DB2 v10.5.0.8</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -13181,7 +13185,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>453.46</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13193,17 +13197,17 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>156</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>394</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>277</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -13213,14 +13217,14 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -13232,27 +13236,19 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>ONPODMCBDP01</t>
+          <t>ONPODMSBDP01</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>42.87</t>
-        </is>
-      </c>
+      <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>5.79</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
+          <t>510.75</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13265,14 +13261,10 @@
           <t>RESDB</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DB2 v10.5.0.8</t>
+          <t>DB2 v10.1.0.5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -13284,7 +13276,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>453.46</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13296,17 +13288,17 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>235</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>567</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>303</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -13316,14 +13308,14 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -13335,19 +13327,27 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>ONPODMSBDP01</t>
+          <t>ONPODMCBDP01</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>42.87</t>
+        </is>
+      </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>510.75</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr"/>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13852,7 +13852,11 @@
           <t>SIGA_1782</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>SQL Server 2022</t>
@@ -13923,7 +13927,11 @@
           <t>SIGA_55</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>SQL Server 2022</t>
@@ -14050,7 +14058,11 @@
           <t>SIGA_55</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>SQL Server 2008 R2</t>
